--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -616,14 +634,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -643,12 +661,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +683,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -677,8 +701,11 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -692,6 +719,9 @@
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,11 +735,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -728,7 +758,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -739,10 +769,10 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
@@ -1079,10 +1109,8 @@
           <t>Shiwangi kumari Nath</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9741662373</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9741662373</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1145,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.691217</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.691217</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1168,47 +1194,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L24-6</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.340672</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.340672</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>23h 23m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>23h 23m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>23h 23m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>23h 23m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -1217,6 +1239,214 @@
       <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372843</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Sudha Rai</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Sudha Rai</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9848871338</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:37 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>LTP9848871338</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:29:28 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 10:06:37 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Pimbahal Pokhari, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>06:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>20h 37m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -781,7 +781,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1309,10 +1309,8 @@
           <t>Sudha Rai</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9848871338</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9848871338</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1402,10 +1400,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1416,7 +1412,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -590,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -630,23 +630,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -661,10 +684,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -699,29 +722,61 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Location Shifting</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -748,12 +803,12 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -763,14 +818,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -781,12 +836,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1446,6 +1501,1258 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372830</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Prem Krishna Maharjan</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Prem Krishna Maharjan</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9802079732</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:04:56 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9851033710</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 01:15:04 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:04:56 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>27.648262, 85.339322, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>07:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 49m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:14 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>No signal</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372882</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Gupta</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Gupta</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9828550452</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:14:20 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>LTP9812956405</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 02:14:18 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:14:20 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa Woda n : Municipality:: lalitpur Landmark:daraz office, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB179</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372976</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Prasad Pathak</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Prasad Pathak</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851198825</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:13:37 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851198825</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:48:58 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:13:37 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.71476</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu ,woda 6,Jorpati near Footsal arena, Patitar, Boudha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>bishnupath@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>05:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L40-3</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.36281</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>19h 24m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372568</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Shiwangi kumari Nath</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Shiwangi kumari Nath</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9741662373</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12:51 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9741662373S</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:31:43 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12:51 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.691217</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>M Shanti Chock - Palace Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>10:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L24-6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.340672</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 41m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372958</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Raj Bhul</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Raj Bhul</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9805674711</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12:03 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9805674711</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:35:26 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:12:03 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing Chowk ,kapan, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>rit09.np@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>05:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L63-6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>19h 36m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:05 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1369621</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:11:15 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 07:58:45 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:11:15 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Location Shifting</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Karki</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>3d 15h 12m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -836,7 +836,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1568,10 +1568,8 @@
           <t>Prem Krishna Maharjan</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9802079732</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9802079732</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1657,10 +1655,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1671,7 +1667,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1772,10 +1768,8 @@
           <t>Rupesh Gupta</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9828550452</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9828550452</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1843,10 +1837,8 @@
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
@@ -1865,10 +1857,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1879,7 +1869,7 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : No signal  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1980,10 +1970,8 @@
           <t>Bishnu Prasad Pathak</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851198825</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851198825</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2018,10 +2006,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.71476</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.71476</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2077,25 +2063,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L40-3</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.36281</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.36281</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2196,10 +2178,8 @@
           <t>Shiwangi kumari Nath</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9741662373</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9741662373</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2234,10 +2214,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.691217</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.691217</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2289,25 +2267,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L24-6</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.340672</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.340672</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2408,10 +2382,8 @@
           <t>Raj Bhul</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9805674711</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9805674711</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2501,10 +2473,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2515,7 +2485,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2606,20 +2576,14 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2705,10 +2669,8 @@
           <t>Bishal Karki</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2719,7 +2681,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,54 +528,72 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chandramani Tharu</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -722,13 +746,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>5</v>
+      <c r="E2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -738,12 +765,15 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -754,12 +784,15 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -770,13 +803,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>7</v>
+      <c r="E5" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -824,7 +860,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
     <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -836,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2715,6 +2751,438 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372940</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Satyam Pratiraj</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Satyam Pratiraj</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9865067783</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:06:26 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9865067783</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:06:26 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:38:00 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.67219</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, kritipur, near at Town Planning Park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>satyam.chrombit@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.28124</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>20h 31m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>20h 31m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372940</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Satyam Pratiraj</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Satyam Pratiraj</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9865067783</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:06:26 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9865067783</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:06:26 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:38:00 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.67219</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, kritipur, near at Town Planning Park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>satyam.chrombit@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>06:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.28124</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>20h 31m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 31m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2808,20 +2808,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Satyam Pratiraj</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9865067783</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9865067783</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2856,10 +2850,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.67219</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.67219</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2915,25 +2907,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.28124</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.28124</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3024,20 +3012,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Satyam Pratiraj</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9865067783</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9865067783</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3072,10 +3054,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.67219</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.67219</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3131,25 +3111,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.28124</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.28124</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -580,20 +580,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -675,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +754,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -754,8 +778,11 @@
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>6</v>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +800,10 @@
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -792,7 +822,10 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,7 +845,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -872,7 +908,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3159,6 +3195,214 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:56 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371605</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Ramita Pujari</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9818579073</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 11:27:33 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 12:56:49 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.711797</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Stationery &amp; Gift Center, P863+MPJ, Purano Dhalko Marg, Kathmandu 44600, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.304165</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -782,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -875,10 +875,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -902,7 +902,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -3262,10 +3262,8 @@
           <t>Ramita Pujari</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9818579073</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9818579073</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3300,10 +3298,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.711797</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.711797</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3351,47 +3347,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.304165</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.304165</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 29m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 29m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 29m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3400,6 +3392,430 @@
       <c r="AX12" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373106</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Piano B Italian Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Piano B Italian Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9802302303</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:05:15 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9803511888</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 05:31:31 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:05:15 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.68331</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Next to  Mangal Decor Sanepa, Lalitpur , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>pianopianosouth@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>05:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB279</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.31069</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>19h 33m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 1:04 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1371820</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Madav Nepal</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Madav Nepal</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9767384015</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:04:34 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>BKT9767384015</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>15 Oct 2026 02:23:45 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:04:34 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>27.668574009940066, 85.37675397961262 GPS Coordinates Nearest: BKT002-01-1/7-L7-5 (76m Road) Map: CG</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>madhavnepal916@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>18:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L7-7A</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 40m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -908,7 +908,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3462,10 +3462,8 @@
           <t>Piano B Italian Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9802302303</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9802302303</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3500,10 +3498,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.68331</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.68331</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3559,25 +3555,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB279</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.31069</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.31068999999999</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3678,10 +3670,8 @@
           <t>Madav Nepal</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9767384015</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9767384015</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3771,10 +3761,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3785,7 +3773,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -782,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -885,7 +885,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -902,13 +902,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3807,6 +3807,222 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373387</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Maharjan</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9841963286</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>dipeshmaharjan</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 08:46:25 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.67637</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Pulchowk Behind sumeru city hospital, Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>dipesh.click@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>03:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.3146</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>4h 46m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -908,7 +908,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3874,10 +3874,8 @@
           <t>Dipesh Maharjan</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9841963286</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9841963286</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3912,10 +3910,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.67637</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.67637</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3971,25 +3967,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.3146</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.3146</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -776,13 +776,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -830,25 +830,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>12</v>
+      <c r="F6" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -896,7 +918,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -908,7 +930,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4015,6 +4037,434 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:42 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372520</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Sajan Banmala</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Sajan Banmala</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9861343644</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:42:51 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9861343644</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:10:55 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:42:51 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.666626</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Jagati Bus Stand, Araniko Highway, Bhaktapur 44800, 27.66654, 85.43744, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>sajan.banmala123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>14:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L18-6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.437244</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 31m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:36 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372994</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Rohit kumar sah</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Rohit kumar sah</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9766514605</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:36:39 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>LTP9766514605</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 03:56:44 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:36:39 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Sparrow SMS - Telecommunications service provider Lalitpur 44700 , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>rohitsah2058@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>08:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>22h 39m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -776,13 +776,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -832,7 +832,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -852,25 +852,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>14</v>
+      <c r="F7" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -895,7 +917,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -918,7 +940,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4104,10 +4126,8 @@
           <t>Sajan Banmala</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9861343644</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9861343644</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4142,10 +4162,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.666626</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.666626</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4201,25 +4219,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L18-6</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.437244</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.43724400000001</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4320,10 +4334,8 @@
           <t>Rohit kumar sah</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9766514605</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9766514605</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4395,10 +4407,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH17" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
@@ -4417,10 +4427,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4431,37 +4439,1213 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>22h 39m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>No internet</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372714</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>KB Stylish, kausaltar Branch</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>KB Stylish, kausaltar Branch</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9801028227</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:56:15 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>BKT9801028227</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:52:43 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:56:15 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Thimi, Bhaktapur, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9801028227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>13:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L40-6</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>22h 39m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 3m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow internet   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX17" s="3" t="inlineStr">
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:48 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>upgrade to wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373109</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Kunwar</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Kunwar</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851068973</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:48:41 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851068973</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 05:33:17 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:48:41 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>MC26+34Q, F099, Anantalingeshwar,Suryabinayak Municipality Ward 7 Office - Bhaktapur Municipality,</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>isanjaya@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>07:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L1-CDB3</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>21h 15m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade to wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372643</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Adhikari</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Adhikari</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841799665</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:05:39 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9841799665</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:05:39 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:51:24 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.69646</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Himshikhar Boarding School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>bhumiadhikari25@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>13:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.26782</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 45m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 45m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:50 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372412</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Maharjan</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Maharjan</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9843345497</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:45 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9843345497</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:45 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:50:14 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.70441</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Chaauni incessant rain building, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>ashishmahrjan0021@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>14:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.29805</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 52m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 52m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372412</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Maharjan</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Ashish Maharjan</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9843345497</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:45 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9843345497</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 08:57:45 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:50:14 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.70441</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Chaauni incessant rain building, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>ashishmahrjan0021@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>14:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.29805</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 52m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 52m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -952,7 +952,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4540,10 +4540,8 @@
           <t>KB Stylish, kausaltar Branch</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9801028227</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9801028227</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4615,10 +4613,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH18" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
@@ -4637,10 +4633,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4651,7 +4645,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4742,20 +4736,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Sanjay Kunwar</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851068973</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851068973</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4845,10 +4833,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4859,7 +4845,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade to wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -5068,10 +5054,8 @@
           <t>Bhumi Raj Adhikari</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841799665</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841799665</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5106,10 +5090,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.69646</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.69646</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5165,25 +5147,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.26782</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.26782</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5284,10 +5262,8 @@
           <t>Ashish Maharjan</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9843345497</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9843345497</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5322,10 +5298,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.70441</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.70441</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5381,25 +5355,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>1,14</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.29805</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.29805</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5500,10 +5470,8 @@
           <t>Ashish Maharjan</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9843345497</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9843345497</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5538,10 +5506,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.70441</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.70441</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5597,25 +5563,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>1,14</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.29805</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.29805</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -670,42 +670,65 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>63.6%</t>
+      <c r="B4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>88.2%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -720,10 +743,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -776,29 +799,29 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -810,17 +833,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Location Shifting</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -832,7 +855,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -854,7 +877,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Location Shifting</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -874,25 +897,91 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>19</v>
+      <c r="C10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -941,18 +1030,18 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5611,6 +5700,1178 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 3:51 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372703</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sita Nepali</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sita Nepali</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9845802860</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:42:46 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9845802860</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 11:42:46 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:51:50 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.729657</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Samakhusi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>14:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L1-4</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.318584</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 9m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 9m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>5G not working</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373513</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Lila Dulal Neupane</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Lila Dulal Neupane</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9813362762</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:00:46 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9813362762</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 11:01:14 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:00:46 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Capital College &amp; Research Center - Private college M8CW+JJM Surya Kot Marg 35 Kathmandu 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>04:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB332</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>4h 59m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 3:59 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372760</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Thapa</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Thapa</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9841476002</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9841476002</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:24:23 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.67431</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Jadibuti, near at Sindhu Guest House, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>supreetkhadka22@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>13:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.35262</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 34m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372593</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Kafle</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Kafle</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9841350402</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:58:05 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9841350402</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 10:40:56 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:58:05 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.680697</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near to Near Matribhumi School, Madhyapur Thimi, Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>leoprantik10@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>15:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.365577</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 17m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 3:52 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373421</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Kumari Pandey</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Kumari Pandey</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9849156086</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:53:43 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9849156086</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 09:23:06 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 03:53:43 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.683159</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Innovative English School Details from Google Maps M8MJ+GHH, Bibhuti Marg, Kathmandu 44600 +977 1-52</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>kaldelbabu20@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>05:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB061</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.330939</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>6h 30m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -1041,7 +1041,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5767,10 +5767,8 @@
           <t>Sita Nepali</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9845802860</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9845802860</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5805,10 +5803,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.729657</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.729657</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5860,25 +5856,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L1-4</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.318584</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.318584</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5979,10 +5971,8 @@
           <t>Lila Dulal Neupane</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9813362762</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9813362762</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6068,10 +6058,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -6082,7 +6070,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : 5G not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6183,10 +6171,8 @@
           <t>Sunita Thapa</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9841476002</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9841476002</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6221,10 +6207,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.67431</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.67431</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6280,25 +6264,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.35262</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.35262</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6399,10 +6379,8 @@
           <t>Ranjana Kafle</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9841350402</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9841350402</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6437,10 +6415,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.680697</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.680697</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6496,25 +6472,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.365577</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.365577</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6723,10 +6695,8 @@
           <t>Bhim Kumari Pandey</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9849156086</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9849156086</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6761,10 +6731,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.683159</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.683159</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6820,25 +6788,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB061</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.330939</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.330939</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -802,10 +802,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -978,10 +978,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1041,7 +1041,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6836,6 +6836,222 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 4:44 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1372778</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Man Bahadur Dura</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Man Bahadur Dura</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9846190489</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:36:34 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9846190489</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>16 Oct 2026 12:36:34 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 04:44:40 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.72776</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Ichangu, Raniban, Nagarjun Near By Nagarjun - 1 No. Ward Office, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>mangrg209@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>14:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.29223</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 8m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 8m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_17_Oct_2026.xlsx
@@ -1041,7 +1041,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6903,10 +6903,8 @@
           <t>Man Bahadur Dura</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9846190489</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9846190489</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6941,10 +6939,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.72776</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.72776</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -7000,25 +6996,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,14</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.29223</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.29223</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
